--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:26:54+00:00</t>
+    <t>2025-01-23T13:26:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-23T13:26:37+00:00</t>
+    <t>2025-01-24T17:22:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T17:22:23+00:00</t>
+    <t>2025-01-29T14:25:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T14:25:50+00:00</t>
+    <t>2025-01-29T15:50:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T15:50:40+00:00</t>
+    <t>2025-01-30T15:03:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-30T15:03:39+00:00</t>
+    <t>2025-01-31T08:45:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T08:45:39+00:00</t>
+    <t>2025-02-18T10:06:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="213">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T10:06:11+00:00</t>
+    <t>2025-02-18T11:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>participant représente toute personne/structure impliquée dans les évènements décrits par le document qui n’a pas été mentionné ailleurs.</t>
+    <t>L'élément de l'en-tête du CDA participant permet de représenter toute personne/structure impliquée dans les évènements décrits par le document qui n’a pas été mentionné ailleurs.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -391,10 +391,10 @@
     <t>Participant1.typeCode</t>
   </si>
   <si>
-    <t>Type de participation : la valeur doit être issue du JDV_J144_ParticipationType_CISIS (1.2.250.1.213.1.1.5.591)</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J144-ParticipationType-CISIS/FHIR/JDV-J144-ParticipationType-CISIS</t>
+    <t>Type de participation</t>
+  </si>
+  <si>
+    <t>http://hl7.org/cda/stds/core/ValueSet/CDAParticipationType</t>
   </si>
   <si>
     <t>Participant1.contextControlCode</t>
@@ -670,156 +670,6 @@
   </si>
   <si>
     <t>Identification du participant</t>
-  </si>
-  <si>
-    <t>Participant1.associatedEntity.nullFlavor</t>
-  </si>
-  <si>
-    <t>Participant1.associatedEntity.realmCode</t>
-  </si>
-  <si>
-    <t>Participant1.associatedEntity.typeId</t>
-  </si>
-  <si>
-    <t>Participant1.associatedEntity.typeId.nullFlavor</t>
-  </si>
-  <si>
-    <t>Participant1.associatedEntity.typeId.assigningAuthorityName</t>
-  </si>
-  <si>
-    <t>Participant1.associatedEntity.typeId.displayable</t>
-  </si>
-  <si>
-    <t>Participant1.associatedEntity.typeId.root</t>
-  </si>
-  <si>
-    <t>Participant1.associatedEntity.typeId.extension</t>
-  </si>
-  <si>
-    <t>Participant1.associatedEntity.templateId</t>
-  </si>
-  <si>
-    <t>Participant1.associatedEntity.classCode</t>
-  </si>
-  <si>
-    <t>PS / Non PS La valeur doit être issue du JDV_J141_RoleClass_CISIS (1.2.250.1.213.1.1.5.588).</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J141-RoleClass-CISIS/FHIR/JDV-J141-RoleClass-CISIS</t>
-  </si>
-  <si>
-    <t>AssociatedEntity.classCode</t>
-  </si>
-  <si>
-    <t>Participant1.associatedEntity.id</t>
-  </si>
-  <si>
-    <t>Identifiant du participant Obligatoire pour les professionnels</t>
-  </si>
-  <si>
-    <t>AssociatedEntity.id</t>
-  </si>
-  <si>
-    <t>Participant1.associatedEntity.id.nullFlavor</t>
-  </si>
-  <si>
-    <t>Participant1.associatedEntity.id.assigningAuthorityName</t>
-  </si>
-  <si>
-    <t>Participant1.associatedEntity.id.displayable</t>
-  </si>
-  <si>
-    <t>Participant1.associatedEntity.id.root</t>
-  </si>
-  <si>
-    <t>- Pour les professionnels : '1.2.250.1.71.4.2.1' 
-- Pour les autres : libre</t>
-  </si>
-  <si>
-    <t>A unique identifier that guarantees the global uniqueness of the instance identifier. The root alone may be the entire instance identifier.</t>
-  </si>
-  <si>
-    <t>Participant1.associatedEntity.id.extension</t>
-  </si>
-  <si>
-    <t>- Pour les professionnels : Valeur de l’identifiant du professionnel participant. Source : valeur de PS_IdNat (voir annexe [6]) 
-- Pour les autres : libre</t>
-  </si>
-  <si>
-    <t>Participant1.associatedEntity.sdtcIdentifiedBy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/IdentifiedBy
-</t>
-  </si>
-  <si>
-    <t>AssociatedEntity.sdtcIdentifiedBy</t>
-  </si>
-  <si>
-    <t>Participant1.associatedEntity.code</t>
-  </si>
-  <si>
-    <t>Profession / savoir-faire ou rôle : 
-- Facultatif pour les PS, non PS et systèmes 
-- Facultatif pour patient/usager</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J01-XdsAuthorSpecialty-CISIS/FHIR/JDV-J01-XdsAuthorSpecialty-CISIS</t>
-  </si>
-  <si>
-    <t>AssociatedEntity.code</t>
-  </si>
-  <si>
-    <t>Participant1.associatedEntity.addr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/AD
-</t>
-  </si>
-  <si>
-    <t>Adresse géopostale du participant</t>
-  </si>
-  <si>
-    <t>AssociatedEntity.addr</t>
-  </si>
-  <si>
-    <t>Participant1.associatedEntity.telecom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/TEL
-</t>
-  </si>
-  <si>
-    <t>Coordonnées télécom du participant</t>
-  </si>
-  <si>
-    <t>AssociatedEntity.telecom</t>
-  </si>
-  <si>
-    <t>Participant1.associatedEntity.associatedPerson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Person {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-person}
-</t>
-  </si>
-  <si>
-    <t>Identité du participant</t>
-  </si>
-  <si>
-    <t>AssociatedEntity.associatedPerson</t>
-  </si>
-  <si>
-    <t>Participant1.associatedEntity.scopingOrganization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Organization {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-represented-organization}
-</t>
-  </si>
-  <si>
-    <t>Structure</t>
-  </si>
-  <si>
-    <t>AssociatedEntity.scopingOrganization</t>
   </si>
 </sst>
 </file>
@@ -1121,11 +971,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK56"/>
+  <dimension ref="A1:AK34"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="57.4140625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="57.4140625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="44.37109375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="44.37109375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="24.9375" customWidth="true" bestFit="true"/>
@@ -1149,13 +999,13 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="97.74609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="87.015625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="35.75390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="30.9921875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -4640,2242 +4490,6 @@
         <v>74</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="C35" s="2"/>
-      <c r="D35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="F35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K35" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L35" s="2"/>
-      <c r="M35" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
-      <c r="P35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q35" s="2"/>
-      <c r="R35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y35" s="2"/>
-      <c r="Z35" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AG35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="C36" s="2"/>
-      <c r="D36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E36" s="2"/>
-      <c r="F36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K36" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="L36" s="2"/>
-      <c r="M36" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
-      <c r="P36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q36" s="2"/>
-      <c r="R36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AG36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK36" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="C37" s="2"/>
-      <c r="D37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E37" s="2"/>
-      <c r="F37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K37" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="L37" s="2"/>
-      <c r="M37" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
-      <c r="P37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q37" s="2"/>
-      <c r="R37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AG37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="C38" s="2"/>
-      <c r="D38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="F38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K38" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L38" s="2"/>
-      <c r="M38" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
-      <c r="P38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q38" s="2"/>
-      <c r="R38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X38" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y38" s="2"/>
-      <c r="Z38" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="C39" s="2"/>
-      <c r="D39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E39" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="F39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K39" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="L39" s="2"/>
-      <c r="M39" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
-      <c r="P39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q39" s="2"/>
-      <c r="R39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AG39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="C40" s="2"/>
-      <c r="D40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E40" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="F40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K40" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="L40" s="2"/>
-      <c r="M40" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
-      <c r="P40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q40" s="2"/>
-      <c r="R40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="C41" s="2"/>
-      <c r="D41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E41" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="F41" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G41" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K41" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L41" s="2"/>
-      <c r="M41" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
-      <c r="P41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q41" s="2"/>
-      <c r="R41" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="S41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AG41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK41" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="C42" s="2"/>
-      <c r="D42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E42" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="F42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K42" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="L42" s="2"/>
-      <c r="M42" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
-      <c r="P42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q42" s="2"/>
-      <c r="R42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK42" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="C43" s="2"/>
-      <c r="D43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E43" s="2"/>
-      <c r="F43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K43" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="L43" s="2"/>
-      <c r="M43" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
-      <c r="P43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q43" s="2"/>
-      <c r="R43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="C44" s="2"/>
-      <c r="D44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E44" s="2"/>
-      <c r="F44" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G44" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K44" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="M44" s="2"/>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
-      <c r="P44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q44" s="2"/>
-      <c r="R44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y44" s="2"/>
-      <c r="Z44" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="C45" s="2"/>
-      <c r="D45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E45" s="2"/>
-      <c r="F45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K45" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="M45" s="2"/>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
-      <c r="P45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q45" s="2"/>
-      <c r="R45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="C46" s="2"/>
-      <c r="D46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="F46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K46" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L46" s="2"/>
-      <c r="M46" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
-      <c r="P46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q46" s="2"/>
-      <c r="R46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y46" s="2"/>
-      <c r="Z46" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="C47" s="2"/>
-      <c r="D47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E47" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="F47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G47" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K47" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="L47" s="2"/>
-      <c r="M47" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
-      <c r="P47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q47" s="2"/>
-      <c r="R47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="C48" s="2"/>
-      <c r="D48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E48" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="F48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G48" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K48" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="L48" s="2"/>
-      <c r="M48" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
-      <c r="P48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q48" s="2"/>
-      <c r="R48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AG48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="C49" s="2"/>
-      <c r="D49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E49" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="F49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G49" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K49" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
-      <c r="P49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q49" s="2"/>
-      <c r="R49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E50" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="F50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
-      <c r="P50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q50" s="2"/>
-      <c r="R50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="L51" s="2"/>
-      <c r="M51" s="2"/>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
-      <c r="P51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q51" s="2"/>
-      <c r="R51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="M52" s="2"/>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
-      <c r="P52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q52" s="2"/>
-      <c r="R52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y52" s="2"/>
-      <c r="Z52" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="C53" s="2"/>
-      <c r="D53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="M53" s="2"/>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
-      <c r="P53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q53" s="2"/>
-      <c r="R53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="C54" s="2"/>
-      <c r="D54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G54" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K54" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="M54" s="2"/>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
-      <c r="P54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q54" s="2"/>
-      <c r="R54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="C55" s="2"/>
-      <c r="D55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E55" s="2"/>
-      <c r="F55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G55" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K55" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="M55" s="2"/>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
-      <c r="P55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q55" s="2"/>
-      <c r="R55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="C56" s="2"/>
-      <c r="D56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E56" s="2"/>
-      <c r="F56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G56" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K56" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="M56" s="2"/>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
-      <c r="P56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q56" s="2"/>
-      <c r="R56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T11:00:40+00:00</t>
+    <t>2025-02-18T15:10:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:10:02+00:00</t>
+    <t>2025-02-18T15:17:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:17:48+00:00</t>
+    <t>2025-02-18T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:09+00:00</t>
+    <t>2025-02-18T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:38+00:00</t>
+    <t>2025-02-18T15:24:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:24:54+00:00</t>
+    <t>2025-02-18T15:28:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:28:32+00:00</t>
+    <t>2025-02-18T15:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:29:38+00:00</t>
+    <t>2025-02-18T15:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:04+00:00</t>
+    <t>2025-02-18T15:30:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:23+00:00</t>
+    <t>2025-02-18T15:30:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:53+00:00</t>
+    <t>2025-02-20T13:34:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:34:17+00:00</t>
+    <t>2025-02-20T13:46:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:46:00+00:00</t>
+    <t>2025-02-20T13:48:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:48:47+00:00</t>
+    <t>2025-02-20T13:50:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:16+00:00</t>
+    <t>2025-02-20T13:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:51+00:00</t>
+    <t>2025-02-20T13:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:51:52+00:00</t>
+    <t>2025-02-20T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:17+00:00</t>
+    <t>2025-02-20T13:53:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:53+00:00</t>
+    <t>2025-02-20T14:37:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:37:28+00:00</t>
+    <t>2025-02-20T14:38:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:00+00:00</t>
+    <t>2025-02-20T14:38:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:23+00:00</t>
+    <t>2025-02-20T14:42:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:14+00:00</t>
+    <t>2025-02-20T14:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:55+00:00</t>
+    <t>2025-02-20T14:43:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:43:30+00:00</t>
+    <t>2025-02-20T14:45:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:45:32+00:00</t>
+    <t>2025-02-20T14:47:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:47:06+00:00</t>
+    <t>2025-02-20T14:48:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:48:16+00:00</t>
+    <t>2025-02-20T15:31:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T15:31:18+00:00</t>
+    <t>2025-02-21T13:12:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T13:12:29+00:00</t>
+    <t>2025-02-21T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T15:18:09+00:00</t>
+    <t>2025-02-23T14:02:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-23T14:02:58+00:00</t>
+    <t>2025-02-24T10:33:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T10:33:29+00:00</t>
+    <t>2025-02-24T11:08:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T11:08:59+00:00</t>
+    <t>2025-02-24T14:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T14:08:41+00:00</t>
+    <t>2025-02-25T09:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
